--- a/docs/PyTortoiseGit_功能测试用例.xlsx
+++ b/docs/PyTortoiseGit_功能测试用例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$J$155</definedName>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8552,6 +8552,5362 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TC-GEN-001</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>语言</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>切换界面语言</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1.打开设置-常规；2.语言下拉选 English；3.确定；4.重开设置</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>界面文案切换为英文；QSettings language=English；重开仍为英文</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>验证语言即时切换与持久化</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TC-GEN-002</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>自动检查新版本</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>每周自动检查新版本开关</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1.勾选/取消该复选框；2.确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>QSettings checkNewer 与勾选一致并回显（占位，不发起联网）</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>验证开关持久化</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TC-GEN-003</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>立即检查</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Check now 占位提示</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1.点击“立即检查”；2.关闭提示</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>弹出占位说明对话框，不崩溃、不改配置</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>验证占位按钮行为</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TC-GEN-004</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>首次启动向导</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>重新运行首次启动向导</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1.点击“重新运行首次启动向导”</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>打开 FirstStartWizard 向导窗口</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>验证向导入口</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TC-GEN-005</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>创建库</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Create Library 占位提示</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>1.点击“创建库”</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>弹出占位说明对话框，不崩溃</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>验证占位按钮行为</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TC-GEN-006</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Git 路径</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>浏览选择 Git 目录</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1.点击 Git 路径后的“...”；2.选择目录</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>所选目录回填到 Git.exe 路径输入框</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>验证目录选择</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TC-GEN-007</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Git 路径</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>立即检查 Git 版本</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>已安装 git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1.填入有效 git.exe 路径；2.点击“立即检查”</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>版本标签显示 git version x.y.z</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>验证版本探测</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>E2E(QTest+真实 git)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TC-GEN-008</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Git 路径</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>无效路径检查容错</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1.填入不存在路径；2.点击“立即检查”</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>版本标签清空，不抛异常</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>验证错误容错</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TC-GEN-009</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Git 路径</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>gitPath 生效于运行层</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>已保存 gitPath</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1.保存 gitPath；2.调用 find_git_executable()</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>返回所保存的 git 可执行文件路径</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>验证配置被运行层消费</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TC-GEN-010</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>额外 PATH</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>extraPath 注入子进程 PATH</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>已保存 extraPath</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1.保存 extraPath；2.构造 GitRunner；3.读取 env[PATH]</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>env[PATH] 以 extraPath 开头（后接原 PATH）</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>验证配置被运行层消费</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TC-GEN-011</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>环境变量</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>显示环境变量</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1.点击“显示环境变量”</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>弹出包含 KEY=VALUE 列表的信息框</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>验证环境变量展示</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-001</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>第一层列表</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>默认勾选第一层命令</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>未保存过设置</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1.打开设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>默认勾选 Sync/CreateRepo/Clone/Commit 四项</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>验证原版默认值</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-002</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>第一层列表</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>勾选项显示在第一层菜单</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1.勾选“Push”；2.确定；3.对仓库右键</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>右键菜单第一层出现 Push</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>验证过滤生效</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>E2E(QTest+真实仓库)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-003</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>第一层列表</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>取消勾选项不出现在第一层</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1.取消“Commit”勾选；2.确定；3.右键</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>第一层不出现 Commit</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>验证取消勾选生效</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-004</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>第一层列表</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>全选/取消全选</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1.点击“全选/取消全选”</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>列表所有项勾选状态同步切换</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>验证批量勾选</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-005</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>第一层列表</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>已修改勾选</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>1.修改勾选；2.点击“恢复默认”</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>恢复为默认四项</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>验证恢复默认</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-006</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>第一层列表</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>勾选持久化</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>1.修改勾选；2.确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>勾选状态与修改一致</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>验证持久化</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-007</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>未版本化路径</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>未版本化路径隐藏菜单</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>1.勾选“未受版本控制的路径隐藏菜单”；2.对未跟踪文件右键</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>不显示 TortoiseGit 菜单</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>验证隐藏逻辑</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-008</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>路径排除</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>排除路径不显示菜单</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1.在路径框填入某目录；2.确定；3.对该目录右键</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>不显示 TortoiseGit 菜单</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>验证路径排除</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU-009</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>拖放菜单</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>启用拖放右键菜单持久化</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1.勾选/取消“启用拖放右键菜单”；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>QSettings EnableDragContextMenu 与勾选一致并回显</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>验证开关持久化</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU2-001</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>设置-右键菜单2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>隐藏列表</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>默认勾选隐藏项</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>未保存过设置</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1.打开设置-右键菜单2</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>默认勾选 SVNIgnore/StashApply/SubmoduleSync</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>验证原版默认值</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU2-002</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>设置-右键菜单2</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>隐藏列表</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>勾选项默认隐藏 Shift 显示</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1.勾选某命令；2.确定；3.不按 Shift 右键；4.按住 Shift 右键</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>不按 Shift 不显示该命令；按住 Shift 显示</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>验证 Shift 扩展逻辑</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>E2E(QTest+真实仓库)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU2-003</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>设置-右键菜单2</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>隐藏列表</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>取消勾选始终显示</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1.取消某命令勾选；2.确定；3.右键</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>始终显示该命令</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>验证取消隐藏</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>TC-CTXMENU2-004</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>设置-右键菜单2</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>隐藏列表</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>全选/恢复默认/持久化</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>设置对话框可打开</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>1.点全选；2.点恢复默认；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>勾选状态正确切换并持久化</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>验证批量与持久化</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>TC-WIN11-001</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>设置-Win11右键菜单</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>显示说明标签</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Windows 11 且设置可打开</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1.打开设置-Win11右键菜单</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>显示“未勾选的项不会显示在顶层菜单…”提示</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>验证提示标签</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TC-WIN11-002</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>设置-Win11右键菜单</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>列表</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>顶层菜单勾选列表（待实现）</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Windows 11</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1.打开设置-Win11右键菜单</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>当前列表未填充、注册按钮为占位（待实现）</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>记录缺口</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TC-DLG1-001</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>日志条数上限</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>设置“日志条数上限”并持久化</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1.修改“日志条数上限”（IDC_DEFAULT_NUMBER_OF）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>QSettings NumberOfLogs 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TC-DLG1-002</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>日志条数单位</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>设置“日志条数单位”并持久化</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>1.修改“日志条数单位”（IDC_DEFAULT_SCALE）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>QSettings NumberOfLogsScale 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TC-DLG1-003</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>日志字体</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>设置“日志字体”并持久化</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>1.修改“日志字体”（IDC_FONTNAMES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>QSettings LogFontName 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TC-DLG1-004</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>日志字号</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>设置“日志字号”并持久化</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>1.修改“日志字号”（IDC_FONTSIZES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>QSettings LogFontSize 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TC-DLG1-005</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>短日期/时间格式</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>设置“短日期/时间格式”并持久化</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>1.修改“短日期/时间格式”（IDC_SHORTDATEFORMAT）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>QSettings LogDateFormat 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TC-DLG1-006</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>相对时间</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>设置“相对时间”并持久化</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1.修改“相对时间”（IDC_RELATIVETIMES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>QSettings RelativeTimes 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TC-DLG1-007</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>星号日志前缀</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>设置“星号日志前缀”并持久化</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>1.修改“星号日志前缀”（IDC_ASTERISKLOGPREFIX）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>QSettings AsteriskLogPrefix 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TC-DLG1-008</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>系统区域日期</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>设置“系统区域日期”并持久化</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1.修改“系统区域日期”（IDC_SYSTEMLOCALEFORDATES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>QSettings UseSystemLocaleForDates 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TC-DLG1-009</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>双击比较上一版</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>设置“双击比较上一版”并持久化</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1.修改“双击比较上一版”（IDC_DIFFBYDOUBLECLICK）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>QSettings DiffByDoubleClickInLog 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TC-DLG1-010</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>缩写重命名</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>设置“缩写重命名”并持久化</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>1.修改“缩写重命名”（IDC_ABBREVIATERENAMINGS）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>QSettings AbbreviateRenamings 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TC-DLG1-011</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>符号化引用名</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>设置“符号化引用名”并持久化</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>1.修改“符号化引用名”（IDC_SYMBOLIZEREFNAMES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>QSettings SymbolizeRefNames 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TC-DLG1-012</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>启用日志缓存</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>设置“启用日志缓存”并持久化</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>1.修改“启用日志缓存”（IDC_ENABLELOGCACHE）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>QSettings EnableLogCache 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TC-DLG1-013</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>启用 Gravatar</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>设置“启用 Gravatar”并持久化</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>1.修改“启用 Gravatar”（IDC_ENABLEGRAVATAR）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>QSettings EnableGravatar 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TC-DLG1-014</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Gravatar URL</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>设置“Gravatar URL”并持久化</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>1.修改“Gravatar URL”（IDC_GRAVATARURL）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>QSettings GravatarUrl 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TC-DLG1-015</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>右侧绘制标签/分支</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>设置“右侧绘制标签/分支”并持久化</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>1.修改“右侧绘制标签/分支”（IDC_RIGHTSIDEBRANCHESTAGS）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>QSettings DrawTagsBranchesOnRightSide 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TC-DLG1-016</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>显示主题和正文</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>设置“显示主题和正文”并持久化</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>1.修改“显示主题和正文”（IDC_FULLCOMMITMESSAGEONLOGLINE）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>QSettings FullCommitMessageOnLogLine 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TC-DLG1-017</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>显示分支修订号</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>设置“显示分支修订号”并持久化</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>1.修改“显示分支修订号”（IDC_SHOWREVCOUNTER）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>QSettings ShowBranchRevisionNumber 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TC-DLG1-018</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>在日志中显示 describe</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>设置“在日志中显示 describe”并持久化</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>1.修改“在日志中显示 describe”（IDC_SHOWDESCRIBE）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>QSettings ShowDescribe 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TC-DLG1-019</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Describe 策略</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>设置“Describe 策略”并持久化</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>1.修改“Describe 策略”（IDC_DESCRIBESTRATEGY）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>QSettings DescribeStrategy 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TC-DLG1-020</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Describe 缩写长度</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>设置“Describe 缩写长度”并持久化</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>1.修改“Describe 缩写长度”（IDC_DESCRIBEABBREVIATEDSIZE）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>QSettings DescribeAbbreviatedSize 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TC-DLG1-021</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>始终显示长格式</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>设置“始终显示长格式”并持久化</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>1.修改“始终显示长格式”（IDC_DESCRIBEALWAYSLONG）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>QSettings DescribeAlwaysLong 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TC-DLG1-022</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>仅跟随第一父提交</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>设置“仅跟随第一父提交”并持久化</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>设置-对话框1 可打开</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>1.修改“仅跟随第一父提交”（IDC_DESCRIBEONLYFIRSTPARENT）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>QSettings DescribeOnlyFollowFirstParent 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TC-DLG2-001</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>自动关闭 git 对话框</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>设置“自动关闭 git 对话框”并持久化</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>1.修改“自动关闭 git 对话框”（IDC_AUTOCLOSECOMBO）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>QSettings AutoCloseGitProgress 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TC-DLG2-002</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>还原时使用回收站</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>设置“还原时使用回收站”并持久化</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>1.修改“还原时使用回收站”（IDC_USERECYCLEBIN）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>QSettings RevertWithRecycleBin 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TC-DLG2-003</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>结束 git 进程前确认</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>设置“结束 git 进程前确认”并持久化</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>1.修改“结束 git 进程前确认”（IDC_CONFIRMKILLPROCESS）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>QSettings ConfirmKillProcess 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TC-DLG2-004</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>随机化同步对话框位置</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>设置“随机化同步对话框位置”并持久化</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>1.修改“随机化同步对话框位置”（IDC_SYNCDIALOGRANDOMPOS）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>QSettings SyncDialogRandomPos 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TC-DLG2-005</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>隐藏未变更引用</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>设置“隐藏未变更引用”并持久化</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>1.修改“隐藏未变更引用”（IDC_REFCOMPAREHIDEUNCHANGED）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>QSettings RefCompareHideUnchanged 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TC-DLG2-006</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>显示 git.exe 执行耗时</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>设置“显示 git.exe 执行耗时”并持久化</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>1.修改“显示 git.exe 执行耗时”（IDC_PROGRESSDLG_SHOW_TIMES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>QSettings ShowGitexeTimings 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TC-DLG2-007</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>标签列表倒序</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>设置“标签列表倒序”并持久化</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>1.修改“标签列表倒序”（IDC_SORTTAGSREVERSED）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>QSettings SortTagsReversed 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TC-DLG2-008</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>禁用声音</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>设置“禁用声音”并持久化</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>1.修改“禁用声音”（IDC_NOSOUNDS）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>QSettings NoSounds 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TC-DLG2-009</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>分支框含 FETCH_HEAD</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>设置“分支框含 FETCH_HEAD”并持久化</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>1.修改“分支框含 FETCH_HEAD”（IDC_BRANCHESINCLUDEFETCHHEAD）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>QSettings BranchesIncludeFetchHead 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TC-DLG2-010</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>使用 .mailmap</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>设置“使用 .mailmap”并持久化</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>1.修改“使用 .mailmap”（IDC_USEMAILMAP）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>QSettings UseMailmap 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TC-DLG2-011</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>自动补全</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>设置“自动补全”并持久化</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>1.修改“自动补全”（IDC_AUTOCOMPLETION）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>QSettings Autocompletion 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TC-DLG2-012</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>补全超时秒数</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>设置“补全超时秒数”并持久化</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>1.修改“补全超时秒数”（IDC_AUTOCOMPLETIONTIMEOUT）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>QSettings AutocompleteParseTimeout 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TC-DLG2-013</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>历史最大条数</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>设置“历史最大条数”并持久化</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>1.修改“历史最大条数”（IDC_MAXHISTORY）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>QSettings MaxHistoryItems 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TC-DLG2-014</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>自动选择项</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>设置“自动选择项”并持久化</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>1.修改“自动选择项”（IDC_SELECTFILESONCOMMIT）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>QSettings SelectFilesForCommit 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>TC-DLG2-015</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>自动选择缺失文件</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>设置“自动选择缺失文件”并持久化</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>1.修改“自动选择缺失文件”（IDC_NOAUTOSELECTMISSING）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>QSettings AutoselectMissingFiles 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>TC-DLG2-016</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>去掉 # 开头行</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>设置“去掉 # 开头行”并持久化</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>设置-对话框2 可打开</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>1.修改“去掉 # 开头行”（IDC_STRIPCOMMENTEDLINES）；2.点确定；3.重开设置</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>QSettings StripCommentedLines 写入所选值；重开回显一致</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>验证选项读写</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TC-DLG3-001</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>配置来源</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>配置来源单选持久化</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>1.选择“全局”；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>QSettings Dialogs3ConfigSource=3；重开仍为“全局”</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>验证单选持久化</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>TC-DLG3-002</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>项目语言</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>项目语言下拉持久化</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>1.语言下拉选 English；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>QSettings ProjectLanguage 对应索引并回显</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>验证下拉持久化</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>TC-DLG3-003</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>最小字符数</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>提交信息最小字符数</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>1.填入 10；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>QSettings LogMinSize=10 并回显</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>验证数值持久化</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>TC-DLG3-004</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>边框位置</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>提交文本框边框位置</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>1.填入 80；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>QSettings LogWidthMarker=80 并回显</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>验证数值持久化</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>TC-DLG3-005</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Signed-Off-By</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>缺少签名警告开关</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>1.下拉选 true；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>QSettings WarnNoSignedOffBy 对应索引并回显</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>验证下拉持久化</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>TC-DLG3-006</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>覆盖图标</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>覆盖图标路径与浏览</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>1.点“...”选择图标；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>路径回填到输入框并持久化 IconFile</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>验证文件选择与持久化</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>TC-DLG3-007</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>保存到</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>保存到下拉</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>设置-对话框3 可打开</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>1.下拉选“本地”；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>下拉选择持久化</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>验证下拉</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>TC-COL1-001</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Conflict</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>修改并持久化 Conflict 颜色</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>1.点击 Conflict 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/Conflict 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>TC-COL1-002</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>修改并持久化 Added 颜色</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>1.点击 Added 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/Added 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>TC-COL1-003</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>修改并持久化 Deleted 颜色</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>1.点击 Deleted 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/Deleted 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>TC-COL1-004</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>修改并持久化 Merged 颜色</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>1.点击 Merged 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/Merged 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>TC-COL1-005</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>修改并持久化 Modified 颜色</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>1.点击 Modified 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/Modified 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>TC-COL1-006</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Renamed</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>修改并持久化 Renamed 颜色</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>1.点击 Renamed 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/Renamed 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>TC-COL1-007</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>NoteNode</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>修改并持久化 NoteNode 颜色</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>1.点击 NoteNode 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/NoteNode 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>TC-COL1-008</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>OtherRef</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>修改并持久化 OtherRef 颜色</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>1.点击 OtherRef 颜色块；2.在色板选择颜色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>颜色块回显所选颜色；QSettings Colors/OtherRef 写入 #RRGGBB</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>TC-COL1-009</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>当前分支颜色</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>当前分支使用本地分支颜色</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>1.勾选该选项；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>QSettings RevGraphUseLocalForCur=True 并回显</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>验证开关持久化</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>TC-COL1-010</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>深色主题</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>深色主题开关</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>设置-颜色1 可打开</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>1.勾选“深色主题”；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>QSettings UseDarkMode=True 并回显</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>验证开关持久化</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>TC-COL1-011</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>恢复默认颜色</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>已修改颜色</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>1.点击“恢复默认”</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>所有颜色块恢复为内置默认色</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>验证恢复默认</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>TC-COL2-001</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>CurrentBranch</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>修改并持久化 CurrentBranch 颜色</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>设置-颜色2 可打开</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>1.点击 CurrentBranch 颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/CurrentBranch 写入</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>TC-COL2-002</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>LocalBranch</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>修改并持久化 LocalBranch 颜色</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>设置-颜色2 可打开</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>1.点击 LocalBranch 颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/LocalBranch 写入</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>TC-COL2-003</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>RemoteBranch</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>修改并持久化 RemoteBranch 颜色</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>设置-颜色2 可打开</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>1.点击 RemoteBranch 颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/RemoteBranch 写入</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>TC-COL2-004</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>修改并持久化 Tag 颜色</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>设置-颜色2 可打开</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>1.点击 Tag 颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/Tag 写入</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>TC-COL2-005</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>FilterMatch</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>修改并持久化 FilterMatch 颜色</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>设置-颜色2 可打开</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>1.点击 FilterMatch 颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/FilterMatch 写入</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>TC-COL2-006</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>恢复默认颜色</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>已修改颜色</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>1.点击“恢复默认”</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>颜色块恢复默认</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>验证恢复默认</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>TC-COL3-001</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>分支线1</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线1颜色</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>1.点击线1颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine1 写入</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>TC-COL3-002</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>分支线2</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线2颜色</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>1.点击线2颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine2 写入</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TC-COL3-003</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>分支线3</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线3颜色</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>1.点击线3颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine3 写入</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>TC-COL3-004</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>分支线4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线4颜色</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>1.点击线4颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine4 写入</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>TC-COL3-005</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>分支线5</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线5颜色</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>1.点击线5颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine5 写入</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>TC-COL3-006</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>分支线6</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线6颜色</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>1.点击线6颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine6 写入</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TC-COL3-007</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>分支线7</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线7颜色</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>1.点击线7颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine7 写入</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>TC-COL3-008</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>分支线8</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>修改并持久化分支线8颜色</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>1.点击线8颜色块；2.选色；3.确定；4.重开</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>颜色回显；QSettings Colors/BranchLine8 写入</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>验证颜色选择与持久化</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>TC-COL3-009</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>线宽</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>日志分支线宽</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>1.线宽下拉选 3；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>QSettings LogLineWidth=3 并回显</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>验证下拉持久化</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>TC-COL3-010</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>节点大小</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>日志节点大小</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>设置-颜色3 可打开</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>1.节点大小下拉选 12；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>QSettings LogNodeSize=12 并回显</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>验证下拉持久化</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>TC-COL3-011</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>恢复默认</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>恢复默认颜色</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>已修改颜色</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>1.点击“恢复默认”</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>8 条分支线颜色恢复默认</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>验证恢复默认</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>TC-ALTED-001</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Notepad</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>选择记事本禁用路径输入</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器可打开</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>1.选择“记事本”</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>自定义路径输入框与“...”按钮置灰</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>验证联动</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>TC-ALTED-002</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>选择自定义启用路径输入</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器可打开</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>1.选择“自定义”</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>路径输入框与“...”按钮可用</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>验证联动</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>TC-ALTED-003</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>路径</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>浏览选择编辑器</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>已选择自定义</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>1.点“...”选择可执行文件</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>路径回填到输入框</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>验证文件选择</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>TC-ALTED-004</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>持久化</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>备用编辑器设置持久化</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器可打开</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>1.选自定义并填路径；2.确定；3.重开</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>单选与路径回显；QSettings AlternativeEditorUseCustom/AlternativeEditor 写入</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>验证持久化</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>E2E(QTest)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8564,7 +13920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8963,22 +14319,231 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>设置-常规</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>设置-右键菜单</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>设置-右键菜单2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>设置-Win11右键菜单</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>设置-对话框1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>设置-对话框2</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>设置-对话框3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>设置-颜色1</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>设置-颜色2</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>设置-颜色3</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>设置-备用编辑器</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>154</v>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>63</v>
+      <c r="B32" t="n">
+        <v>257</v>
+      </c>
+      <c r="C32" t="n">
+        <v>23</v>
+      </c>
+      <c r="D32" t="n">
+        <v>112</v>
+      </c>
+      <c r="E32" t="n">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
